--- a/apps/homework-wordcloud/sample_input/19990103.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990103.xlsx
@@ -2520,12 +2520,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>411194059</t>
+          <t>990094059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>411194059@gms.ndhu.edu.tw</t>
+          <t>990094059@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>411185750</t>
+          <t>990085750</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>411185750@gms.ndhu.edu.tw</t>
+          <t>990085750@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>411123578</t>
+          <t>990023578</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>411123578@gms.ndhu.edu.tw</t>
+          <t>990023578@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>411137045</t>
+          <t>990037045</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>411137045@gms.ndhu.edu.tw</t>
+          <t>990037045@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>411123457</t>
+          <t>990023457</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>411123457@gms.ndhu.edu.tw</t>
+          <t>990023457@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>411153669</t>
+          <t>990053669</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>411153669@gms.ndhu.edu.tw</t>
+          <t>990053669@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>411112230</t>
+          <t>990012230</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>411112230@gms.ndhu.edu.tw</t>
+          <t>990012230@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>411162982</t>
+          <t>990062982</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>411162982@gms.ndhu.edu.tw</t>
+          <t>990062982@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>411148558</t>
+          <t>990048558</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>411148558@gms.ndhu.edu.tw</t>
+          <t>990048558@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>411127143</t>
+          <t>990027143</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>411127143@gms.ndhu.edu.tw</t>
+          <t>990027143@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>411183314</t>
+          <t>990083314</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>411183314@gms.ndhu.edu.tw</t>
+          <t>990083314@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>411168730</t>
+          <t>990068730</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>411168730@gms.ndhu.edu.tw</t>
+          <t>990068730@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>411130882</t>
+          <t>990030882</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>411130882@gms.ndhu.edu.tw</t>
+          <t>990030882@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>411115245</t>
+          <t>990015245</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>411115245@gms.ndhu.edu.tw</t>
+          <t>990015245@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>411118170</t>
+          <t>990018170</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>411118170@gms.ndhu.edu.tw</t>
+          <t>990018170@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>411124949</t>
+          <t>990024949</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>411124949@gms.ndhu.edu.tw</t>
+          <t>990024949@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>411130142</t>
+          <t>990030142</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>411130142@gms.ndhu.edu.tw</t>
+          <t>990030142@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>411135584</t>
+          <t>990035584</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>411135584@gms.ndhu.edu.tw</t>
+          <t>990035584@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>411142934</t>
+          <t>990042934</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>411142934@gms.ndhu.edu.tw</t>
+          <t>990042934@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>411195101</t>
+          <t>990095101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>411195101@gms.ndhu.edu.tw</t>
+          <t>990095101@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>411111664</t>
+          <t>990011664</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>411111664@gms.ndhu.edu.tw</t>
+          <t>990011664@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>411146562</t>
+          <t>990046562</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>411146562@gms.ndhu.edu.tw</t>
+          <t>990046562@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E23" t="n">

--- a/apps/homework-wordcloud/sample_input/19990103.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990103.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>我請AI幫我出練習題，然後自己作答再對答案，這樣複習很有效率。</t>
+          <t>我請AI幫我出練習題，然後自己作答再對答案，這樣複習很有效率。正確率大概是多少？</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>生成式AI很方便，但是我會擔心太依賴它就不會自己思考。</t>
+          <t>生成式AI很方便，但是我會擔心太依賴它就不會自己思考。如果完全不用AI會不會比較好？</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>我請AI幫我出練習題，然後自己作答再對答案，這樣複習很有效率。</t>
+          <t>我請AI幫我出練習題，然後自己作答再對答案，這樣複習很有效率。正確率大概是多少？</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>生成式AI很方便，但是我會擔心太依賴它就不會自己思考。</t>
+          <t>生成式AI很方便，但是我會擔心太依賴它就不會自己思考。如果完全不用AI會不會比較好？</t>
         </is>
       </c>
     </row>
